--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4140973</v>
+        <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>95528</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,26 +703,21 @@
           <t>(Rouy) Greuter &amp; Burdet</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hulebosjön 500 m SV, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447025.6319639772</v>
+        <v>447026</v>
       </c>
       <c r="R2" t="n">
-        <v>6431930.9674396</v>
+        <v>6431931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-01-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-01-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Medobservatör: SN. Yta 1 m2</t>
+          <t>1990-04-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,12 +763,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1, gammal skog</t>
+          <t>Tallmo</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Olof Janson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1437,6 +1413,130 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128416421</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97362</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>552</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cypresslummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium tristachyum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pursh</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hökensås 18 (Hulebosjön 550 m SSV), Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>447202</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6431764</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>F-Hab-0035</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hygge med frötallar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia Lund, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97363</v>
+        <v>97365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97362</v>
+        <v>97364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97365</v>
+        <v>97458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97364</v>
+        <v>97457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97458</v>
+        <v>97470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97457</v>
+        <v>97469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97470</v>
+        <v>97472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97469</v>
+        <v>97471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Lund, Helena Uhlén</t>
+          <t>Helena Uhlén, Sofia Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Uhlén, Sofia Lund</t>
+          <t>Sofia Lund, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97472</v>
+        <v>97473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97471</v>
+        <v>97472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Lund, Helena Uhlén</t>
+          <t>Helena Uhlén, Sofia Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97473</v>
+        <v>97500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97472</v>
+        <v>97499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Uhlén, Sofia Lund</t>
+          <t>Sofia Lund, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97500</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97499</v>
+        <v>97512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97512</v>
+        <v>97516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>156105</v>
       </c>
       <c r="B2" t="n">
-        <v>97517</v>
+        <v>97524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>128416421</v>
       </c>
       <c r="B8" t="n">
-        <v>97516</v>
+        <v>97523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>156105</v>
+        <v>156108</v>
       </c>
       <c r="B2" t="n">
-        <v>97526</v>
+        <v>97992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221940</v>
+        <v>552</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Cypresslummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium zeilleri</t>
+          <t>Lycopodium tristachyum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
+          <t>Pursh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hulebosjön 500 m SV, Vg</t>
+          <t>Hökensås 18 (Hulebosjön 550 m SSV), Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447026</v>
+        <v>447202</v>
       </c>
       <c r="R2" t="n">
-        <v>6431931</v>
+        <v>6431764</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,7 +740,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>F-Hab-0279</t>
+          <t>F-Hab-0035</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88727525</v>
+        <v>88727514</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447049.5459679357</v>
+        <v>447049</v>
       </c>
       <c r="R3" t="n">
-        <v>6431733.608030758</v>
+        <v>6431841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +865,9 @@
           <t>2020-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88727518</v>
+        <v>88727506</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447049.3741007015</v>
+        <v>447038</v>
       </c>
       <c r="R4" t="n">
-        <v>6431840.607391051</v>
+        <v>6431854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,19 +978,9 @@
           <t>2020-10-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88727506</v>
+        <v>88727518</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447037.8769152387</v>
+        <v>447049</v>
       </c>
       <c r="R5" t="n">
-        <v>6431854.002027513</v>
+        <v>6431841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,19 +1091,9 @@
           <t>2020-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88727514</v>
+        <v>88727525</v>
       </c>
       <c r="B6" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1226,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447049.3741007015</v>
+        <v>447050</v>
       </c>
       <c r="R6" t="n">
-        <v>6431840.607391051</v>
+        <v>6431734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,19 +1204,9 @@
           <t>2020-10-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1306,12 +1241,7 @@
         <v>111924490</v>
       </c>
       <c r="B7" t="n">
-        <v>88203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,14 +1270,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hulebotrakten (Hulebotrakten), Vg</t>
+          <t>Hulebotrakten, Hulebotrakten, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447182</v>
+        <v>447183</v>
       </c>
       <c r="R7" t="n">
-        <v>6431751</v>
+        <v>6431750</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1416,57 +1346,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128416421</v>
+        <v>156105</v>
       </c>
       <c r="B8" t="n">
-        <v>97525</v>
+        <v>97993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>552</v>
+        <v>221940</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Mellanlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Lycopodium zeilleri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pursh</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hökensås 18 (Hulebosjön 550 m SSV), Vg</t>
+          <t>Hulebosjön 500 m SV, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447202</v>
+        <v>447026</v>
       </c>
       <c r="R8" t="n">
-        <v>6431764</v>
+        <v>6431931</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,22 +1415,17 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>F-Hab-0035</t>
+          <t>F-Hab-0279</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>1990-04-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hygge med frötallar</t>
+          <t>1990-04-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,15 +1438,20 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallmo</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Lund, Helena Uhlén</t>
+          <t>Olof Janson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 44444-2023 artfynd.xlsx
+++ b/artfynd/A 44444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/156108</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88727514</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88727506</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88727518</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88727525</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111924490</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,8 +1494,22 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/156105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>